--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>4</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>300</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>233.333333333333</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="N15" s="15">
-        <v>233.333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-44.827586206896</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.090909090909</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.230769230769</v>
+        <v>-30.909090909090</v>
       </c>
       <c r="M16" s="15">
-        <v>26.086956521739</v>
+        <v>40.740740740740</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.518518518518</v>
+        <v>-75.483870967741</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-35.714285714285</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G17" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H17" s="15">
-        <v>-15</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="J17" s="14">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K17" s="15">
-        <v>7.272727272727</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.940298507462</v>
+        <v>-5.063291139240</v>
       </c>
       <c r="M17" s="15">
-        <v>136</v>
+        <v>158.620689655172</v>
       </c>
       <c r="N17" s="15">
-        <v>-37.234042553191</v>
+        <v>-30.555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-71.428571428571</v>
+        <v>700</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-22.727272727272</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-23.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-4.166666666666</v>
+        <v>19.230769230769</v>
       </c>
       <c r="M18" s="15">
-        <v>109.090909090909</v>
+        <v>138.461538461538</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.863636363636</v>
+        <v>-71.559633027522</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-27.272727272727</v>
+        <v>25</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.135135135135</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="I19" s="14">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K19" s="15">
-        <v>-38.596491228070</v>
+        <v>-31.147540983606</v>
       </c>
       <c r="L19" s="15">
-        <v>-54.545454545454</v>
+        <v>-50</v>
       </c>
       <c r="M19" s="15">
-        <v>66.666666666666</v>
+        <v>68</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.894736842105</v>
+        <v>2.439024390243</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>-60.869565217391</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I20" s="14">
         <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>-51.851851851851</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="M20" s="15">
-        <v>-27.777777777777</v>
+        <v>-35</v>
       </c>
       <c r="N20" s="15">
-        <v>-77.586206896551</v>
+        <v>-80.882352941176</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-32.608695652173</v>
+        <v>64</v>
       </c>
       <c r="F21" s="17">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G21" s="17">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.758169934640</v>
+        <v>-16.312056737588</v>
       </c>
       <c r="I21" s="17">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="J21" s="17">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.930232558139</v>
+        <v>-12.916666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.806324110671</v>
+        <v>-26.148409893992</v>
       </c>
       <c r="M21" s="18">
-        <v>68.316831683168</v>
+        <v>78.632478632478</v>
       </c>
       <c r="N21" s="18">
-        <v>-59.330143540669</v>
+        <v>-57.259713701431</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
+        <v>11</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
+        <v>22</v>
+      </c>
+      <c r="J23" s="14">
+        <v>20</v>
+      </c>
+      <c r="K23" s="15">
         <v>10</v>
       </c>
-      <c r="H23" s="15">
-        <v>50</v>
-      </c>
-      <c r="I23" s="14">
-        <v>19</v>
-      </c>
-      <c r="J23" s="14">
-        <v>17</v>
-      </c>
-      <c r="K23" s="15">
-        <v>11.764705882352</v>
-      </c>
       <c r="L23" s="15">
-        <v>-58.695652173913</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>-20.833333333333</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>64.705882352941</v>
+        <v>15</v>
       </c>
       <c r="F24" s="14">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G24" s="14">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H24" s="15">
-        <v>28.571428571428</v>
+        <v>22.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="J24" s="14">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="K24" s="15">
-        <v>6.363636363636</v>
+        <v>8.461538461538</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.847457627118</v>
+        <v>0</v>
       </c>
       <c r="M24" s="15">
-        <v>31.460674157303</v>
+        <v>43.877551020408</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F25" s="14">
+        <v>14</v>
+      </c>
+      <c r="G25" s="14">
+        <v>15</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-6.666666666666</v>
+      </c>
+      <c r="I25" s="14">
         <v>25</v>
       </c>
-      <c r="F25" s="14">
-        <v>18</v>
-      </c>
-      <c r="G25" s="14">
-        <v>13</v>
-      </c>
-      <c r="H25" s="15">
-        <v>38.461538461538</v>
-      </c>
-      <c r="I25" s="14">
-        <v>21</v>
-      </c>
       <c r="J25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K25" s="15">
-        <v>23.529411764705</v>
+        <v>25</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.545454545454</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>14.285714285714</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26" s="14">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.529411764705</v>
+        <v>-16.393442622950</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.130434782608</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.25</v>
+        <v>-11.458333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.227272727272</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,22 +1385,22 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
-      </c>
-      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>300</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1412,7 +1412,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L28" s="15">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,39 +1476,39 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L29" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="M29" s="15">
         <v>0</v>
       </c>
-      <c r="M29" s="15">
-        <v>-25</v>
-      </c>
       <c r="N29" s="15">
-        <v>-57.142857142857</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
         <v>-50</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" s="15">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>233.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
         <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.148936170212</v>
+        <v>-25</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.909090909090</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M16" s="15">
-        <v>40.740740740740</v>
+        <v>40</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.483870967741</v>
+        <v>-75.294117647058</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>13.333333333333</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G17" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.416666666666</v>
+        <v>2.127659574468</v>
       </c>
       <c r="I17" s="14">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="J17" s="14">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K17" s="15">
-        <v>7.142857142857</v>
+        <v>8.536585365853</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.063291139240</v>
+        <v>-6.315789473684</v>
       </c>
       <c r="M17" s="15">
-        <v>158.620689655172</v>
+        <v>147.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-30.555555555555</v>
+        <v>-27.049180327868</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>700</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
+        <v>14</v>
+      </c>
+      <c r="G18" s="14">
         <v>19</v>
       </c>
-      <c r="G18" s="14">
-        <v>21</v>
-      </c>
       <c r="H18" s="15">
-        <v>-9.523809523809</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I18" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="L18" s="15">
-        <v>19.230769230769</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>138.461538461538</v>
+        <v>153.846153846154</v>
       </c>
       <c r="N18" s="15">
-        <v>-71.559633027522</v>
+        <v>-74.615384615384</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>25</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.483870967741</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I19" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K19" s="15">
-        <v>-31.147540983606</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L19" s="15">
-        <v>-50</v>
+        <v>-47.252747252747</v>
       </c>
       <c r="M19" s="15">
-        <v>68</v>
+        <v>54.838709677419</v>
       </c>
       <c r="N19" s="15">
-        <v>2.439024390243</v>
+        <v>11.627906976744</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-57.894736842105</v>
+        <v>-12.5</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>-53.571428571428</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="L20" s="15">
-        <v>-55.172413793103</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M20" s="15">
-        <v>-35</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="N20" s="15">
-        <v>-80.882352941176</v>
+        <v>-75.903614457831</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>64</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="F21" s="17">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.312056737588</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I21" s="17">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="J21" s="17">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.916666666666</v>
+        <v>-12.230215827338</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.148409893992</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="M21" s="18">
-        <v>78.632478632478</v>
+        <v>80.740740740740</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.259713701431</v>
+        <v>-56.115107913669</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1197,8 +1197,8 @@
       <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>20</v>
+      <c r="I22" s="14">
+        <v>1</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J23" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>10</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L23" s="15">
-        <v>-54.166666666666</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="M23" s="15">
-        <v>-18.518518518518</v>
+        <v>7.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F24" s="14">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H24" s="15">
-        <v>22.666666666666</v>
+        <v>31.944444444444</v>
       </c>
       <c r="I24" s="14">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="J24" s="14">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="K24" s="15">
-        <v>8.461538461538</v>
+        <v>12.413793103448</v>
       </c>
       <c r="L24" s="15">
-        <v>0</v>
+        <v>3.164556962025</v>
       </c>
       <c r="M24" s="15">
-        <v>43.877551020408</v>
+        <v>53.773584905660</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>-6.666666666666</v>
+        <v>31.25</v>
       </c>
       <c r="I25" s="14">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K25" s="15">
-        <v>25</v>
+        <v>52.173913043478</v>
       </c>
       <c r="L25" s="15">
-        <v>4.166666666666</v>
+        <v>29.629629629629</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,34 +1344,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-46.153846153846</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.393442622950</v>
+        <v>-21.875</v>
       </c>
       <c r="I26" s="14">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="J26" s="14">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="K26" s="15">
-        <v>-19.047619047619</v>
+        <v>-18.103448275862</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.458333333333</v>
+        <v>-12.844036697247</v>
       </c>
       <c r="M26" s="15">
         <v>-16.666666666666</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>200</v>
       </c>
       <c r="F27" s="14">
         <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>133.333333333333</v>
+        <v>250</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L27" s="15">
-        <v>-23.076923076923</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="L28" s="15">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,14 +1466,14 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>2</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1488,10 +1488,10 @@
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="L29" s="15">
         <v>66.666666666666</v>
@@ -1500,39 +1500,39 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
         <v>33.333333333333</v>
@@ -1541,7 +1541,7 @@
         <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
         <v>-50</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
+        <v>200</v>
+      </c>
+      <c r="F15" s="14">
+        <v>8</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="15">
+        <v>166.666666666667</v>
+      </c>
+      <c r="I15" s="14">
+        <v>14</v>
+      </c>
+      <c r="J15" s="14">
+        <v>5</v>
+      </c>
+      <c r="K15" s="15">
+        <v>180</v>
+      </c>
+      <c r="L15" s="15">
+        <v>40</v>
+      </c>
+      <c r="M15" s="15">
+        <v>1300</v>
+      </c>
+      <c r="N15" s="15">
         <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>5</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>150</v>
-      </c>
-      <c r="I15" s="14">
-        <v>11</v>
-      </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
-      <c r="K15" s="15">
-        <v>175</v>
-      </c>
-      <c r="L15" s="15">
-        <v>10</v>
-      </c>
-      <c r="M15" s="15">
-        <v>1000</v>
-      </c>
-      <c r="N15" s="15">
-        <v>83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-90</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I16" s="14">
         <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>-25</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.586206896551</v>
+        <v>-35.384615384615</v>
       </c>
       <c r="M16" s="15">
         <v>40</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.294117647058</v>
+        <v>-77.894736842105</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>8.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F17" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="H17" s="15">
-        <v>2.127659574468</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I17" s="14">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="J17" s="14">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="K17" s="15">
-        <v>8.536585365853</v>
+        <v>5.050505050505</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.315789473684</v>
+        <v>-2.803738317757</v>
       </c>
       <c r="M17" s="15">
-        <v>147.222222222222</v>
+        <v>181.081081081081</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.049180327868</v>
+        <v>-28.275862068965</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.315789473684</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.810810810810</v>
+        <v>-7.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.714285714285</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="M18" s="15">
-        <v>153.846153846154</v>
+        <v>117.647058823529</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.615384615384</v>
+        <v>-75.974025974026</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>14.285714285714</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>-24.137931034482</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J19" s="14">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K19" s="15">
-        <v>-29.411764705882</v>
+        <v>-32.098765432098</v>
       </c>
       <c r="L19" s="15">
-        <v>-47.252747252747</v>
+        <v>-43.298969072165</v>
       </c>
       <c r="M19" s="15">
-        <v>54.838709677419</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>11.627906976744</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>7</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>133.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-12.5</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I20" s="14">
         <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-35.483870967741</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.176470588235</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="M20" s="15">
-        <v>-4.761904761904</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.903614457831</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.894736842105</v>
+        <v>-42.553191489361</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G21" s="17">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.407407407407</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="I21" s="17">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="J21" s="17">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.230215827338</v>
+        <v>-16</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.691358024691</v>
+        <v>-24.166666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>80.740740740740</v>
+        <v>89.583333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.115107913669</v>
+        <v>-57.075471698113</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>-50</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>10</v>
       </c>
       <c r="F23" s="14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H23" s="15">
-        <v>21.428571428571</v>
+        <v>35</v>
       </c>
       <c r="I23" s="14">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J23" s="14">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K23" s="15">
-        <v>15.384615384615</v>
+        <v>19.444444444444</v>
       </c>
       <c r="L23" s="15">
-        <v>-46.428571428571</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="M23" s="15">
-        <v>7.142857142857</v>
+        <v>43.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>60</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="F24" s="14">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G24" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H24" s="15">
-        <v>31.944444444444</v>
+        <v>25.316455696202</v>
       </c>
       <c r="I24" s="14">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="J24" s="14">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K24" s="15">
-        <v>12.413793103448</v>
+        <v>9.302325581395</v>
       </c>
       <c r="L24" s="15">
-        <v>3.164556962025</v>
+        <v>2.732240437158</v>
       </c>
       <c r="M24" s="15">
-        <v>53.773584905660</v>
+        <v>62.068965517241</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>266.666666666667</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>31.25</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I25" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K25" s="15">
-        <v>52.173913043478</v>
+        <v>40.740740740740</v>
       </c>
       <c r="L25" s="15">
-        <v>29.629629629629</v>
+        <v>31.034482758620</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-9.090909090909</v>
+        <v>87.5</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G26" s="14">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.875</v>
+        <v>7.547169811320</v>
       </c>
       <c r="I26" s="14">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="J26" s="14">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.103448275862</v>
+        <v>-10.483870967741</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.844036697247</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.382352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>250</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>160</v>
+        <v>183.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-7.142857142857</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,22 +1435,22 @@
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
         <v>50</v>
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,19 +1479,19 @@
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>66.666666666666</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1511,7 +1511,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
         <v>-100</v>
@@ -1520,19 +1520,19 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>33.333333333333</v>
@@ -1541,7 +1541,7 @@
         <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1634,8 +1634,8 @@
       <c r="K33" s="15">
         <v>-100</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
+        <v>100</v>
+      </c>
+      <c r="M14" s="15">
+        <v>-50</v>
+      </c>
+      <c r="N14" s="15">
         <v>0</v>
-      </c>
-      <c r="M14" s="15">
-        <v>-75</v>
-      </c>
-      <c r="N14" s="15">
-        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="L15" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H16" s="15">
-        <v>-26.923076923076</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="I16" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K16" s="15">
-        <v>-36.363636363636</v>
+        <v>-32.876712328767</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.384615384615</v>
+        <v>-37.179487179487</v>
       </c>
       <c r="M16" s="15">
-        <v>40</v>
+        <v>44.117647058823</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.894736842105</v>
+        <v>-76.213592233009</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-23.529411764705</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="14">
         <v>58</v>
       </c>
       <c r="H17" s="15">
-        <v>-6.896551724137</v>
+        <v>-8.620689655172</v>
       </c>
       <c r="I17" s="14">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="J17" s="14">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="K17" s="15">
-        <v>5.050505050505</v>
+        <v>-1.769911504424</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.803738317757</v>
+        <v>-13.28125</v>
       </c>
       <c r="M17" s="15">
-        <v>181.081081081081</v>
+        <v>158.139534883721</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.275862068965</v>
+        <v>-35.465116279069</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.882352941176</v>
+        <v>46.153846153846</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-7.5</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.904761904761</v>
+        <v>-14</v>
       </c>
       <c r="M18" s="15">
-        <v>117.647058823529</v>
+        <v>138.888888888889</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.974025974026</v>
+        <v>-75.144508670520</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-53.846153846153</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.857142857142</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I19" s="14">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J19" s="14">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K19" s="15">
-        <v>-32.098765432098</v>
+        <v>-27.956989247311</v>
       </c>
       <c r="L19" s="15">
-        <v>-43.298969072165</v>
+        <v>-34.313725490196</v>
       </c>
       <c r="M19" s="15">
-        <v>66.666666666666</v>
+        <v>76.315789473684</v>
       </c>
       <c r="N19" s="15">
-        <v>10</v>
+        <v>24.074074074074</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-35.294117647058</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>-41.176470588235</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L20" s="15">
-        <v>-47.368421052631</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M20" s="15">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N20" s="15">
-        <v>-77.272727272727</v>
+        <v>-73.626373626373</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.553191489361</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="F21" s="17">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G21" s="17">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.461538461538</v>
+        <v>-6.578947368421</v>
       </c>
       <c r="I21" s="17">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="J21" s="17">
-        <v>325</v>
+        <v>367</v>
       </c>
       <c r="K21" s="18">
-        <v>-16</v>
+        <v>-15.258855585831</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.166666666666</v>
+        <v>-24.697336561743</v>
       </c>
       <c r="M21" s="18">
-        <v>89.583333333333</v>
+        <v>94.375</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.075471698113</v>
+        <v>-55.949008498583</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="H22" s="15">
+        <v>200</v>
       </c>
       <c r="I22" s="14">
+        <v>3</v>
+      </c>
+      <c r="J22" s="14">
         <v>1</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="K22" s="15">
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G23" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H23" s="15">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I23" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J23" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K23" s="15">
-        <v>19.444444444444</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.746031746031</v>
+        <v>-38.75</v>
       </c>
       <c r="M23" s="15">
-        <v>43.333333333333</v>
+        <v>48.484848484848</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-7.407407407407</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H24" s="15">
-        <v>25.316455696202</v>
+        <v>8.139534883720</v>
       </c>
       <c r="I24" s="14">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="J24" s="14">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="K24" s="15">
-        <v>9.302325581395</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L24" s="15">
-        <v>2.732240437158</v>
+        <v>6.060606060606</v>
       </c>
       <c r="M24" s="15">
-        <v>62.068965517241</v>
+        <v>62.790697674418</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>57.142857142857</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K25" s="15">
-        <v>40.740740740740</v>
+        <v>25.714285714285</v>
       </c>
       <c r="L25" s="15">
-        <v>31.034482758620</v>
+        <v>41.935483870967</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>87.5</v>
+        <v>-40</v>
       </c>
       <c r="F26" s="14">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>7.547169811320</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="I26" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.483870967741</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.904761904761</v>
+        <v>-15.068493150684</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.382352941176</v>
+        <v>-20</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>266.666666666667</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>183.333333333333</v>
+        <v>157.142857142857</v>
       </c>
       <c r="L27" s="15">
-        <v>21.428571428571</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N29" s="15">
-        <v>-54.545454545454</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-63.636363636363</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>150</v>
+        <v>87.5</v>
       </c>
       <c r="L15" s="15">
         <v>50</v>
@@ -926,7 +926,7 @@
         <v>1400</v>
       </c>
       <c r="N15" s="15">
-        <v>87.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15">
-        <v>-31.034482758620</v>
+        <v>-63.888888888888</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.876712328767</v>
+        <v>-36.144578313253</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.179487179487</v>
+        <v>-38.372093023255</v>
       </c>
       <c r="M16" s="15">
-        <v>44.117647058823</v>
+        <v>29.268292682926</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.213592233009</v>
+        <v>-76.956521739130</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.857142857142</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F17" s="14">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G17" s="14">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.620689655172</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J17" s="14">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.769911504424</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-13.28125</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M17" s="15">
-        <v>158.139534883721</v>
+        <v>153.061224489796</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.465116279069</v>
+        <v>-32.608695652173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F18" s="14">
+        <v>15</v>
+      </c>
+      <c r="G18" s="14">
         <v>19</v>
       </c>
-      <c r="G18" s="14">
-        <v>13</v>
-      </c>
       <c r="H18" s="15">
-        <v>46.153846153846</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="15">
-        <v>-14</v>
+        <v>-12.727272727272</v>
       </c>
       <c r="M18" s="15">
-        <v>138.888888888889</v>
+        <v>100</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.144508670520</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.888888888888</v>
+        <v>-15</v>
       </c>
       <c r="I19" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J19" s="14">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K19" s="15">
-        <v>-27.956989247311</v>
+        <v>-27.722772277227</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.313725490196</v>
+        <v>-37.606837606837</v>
       </c>
       <c r="M19" s="15">
-        <v>76.315789473684</v>
+        <v>73.809523809523</v>
       </c>
       <c r="N19" s="15">
-        <v>24.074074074074</v>
+        <v>21.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>10</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F20" s="14">
+        <v>13</v>
+      </c>
+      <c r="G20" s="14">
+        <v>21</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-38.095238095238</v>
+      </c>
+      <c r="I20" s="14">
+        <v>26</v>
+      </c>
+      <c r="J20" s="14">
+        <v>49</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-46.938775510204</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-44.680851063829</v>
+      </c>
+      <c r="M20" s="15">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-20</v>
-      </c>
-      <c r="F20" s="14">
-        <v>12</v>
-      </c>
-      <c r="G20" s="14">
-        <v>13</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-7.692307692307</v>
-      </c>
-      <c r="I20" s="14">
-        <v>24</v>
-      </c>
-      <c r="J20" s="14">
-        <v>39</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-38.461538461538</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-45.454545454545</v>
-      </c>
-      <c r="M20" s="15">
-        <v>9.090909090909</v>
-      </c>
       <c r="N20" s="15">
-        <v>-73.626373626373</v>
+        <v>-73.737373737373</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.904761904761</v>
+        <v>-39.583333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="G21" s="17">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.578947368421</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="I21" s="17">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="J21" s="17">
-        <v>367</v>
+        <v>415</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.258855585831</v>
+        <v>-17.831325301204</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.697336561743</v>
+        <v>-24.557522123893</v>
       </c>
       <c r="M21" s="18">
-        <v>94.375</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-55.949008498583</v>
+        <v>-56.113256113256</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F23" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>24</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I23" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J23" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>16.666666666666</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L23" s="15">
-        <v>-38.75</v>
+        <v>-38.823529411764</v>
       </c>
       <c r="M23" s="15">
-        <v>48.484848484848</v>
+        <v>36.842105263157</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.166666666666</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F24" s="14">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>8.139534883720</v>
+        <v>8.045977011494</v>
       </c>
       <c r="I24" s="14">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="J24" s="14">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="K24" s="15">
-        <v>7.142857142857</v>
+        <v>6.451612903225</v>
       </c>
       <c r="L24" s="15">
-        <v>6.060606060606</v>
+        <v>1.315789473684</v>
       </c>
       <c r="M24" s="15">
-        <v>62.790697674418</v>
+        <v>62.676056338028</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>27.777777777777</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J25" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K25" s="15">
-        <v>25.714285714285</v>
+        <v>24.390243902439</v>
       </c>
       <c r="L25" s="15">
-        <v>41.935483870967</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>23</v>
+      </c>
+      <c r="D26" s="14">
         <v>12</v>
       </c>
-      <c r="D26" s="14">
-        <v>20</v>
-      </c>
       <c r="E26" s="15">
-        <v>-40</v>
+        <v>91.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.538461538461</v>
+        <v>23.529411764705</v>
       </c>
       <c r="I26" s="14">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="J26" s="14">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.888888888888</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.068493150684</v>
+        <v>-10.303030303030</v>
       </c>
       <c r="M26" s="15">
-        <v>-20</v>
+        <v>-16.853932584269</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>157.142857142857</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
         <v>28.571428571428</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>133.333333333333</v>
+        <v>77.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>55.555555555555</v>
+        <v>45.454545454545</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,23 +1466,23 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1500,30 +1500,30 @@
         <v>20</v>
       </c>
       <c r="N29" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-64.285714285714</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,26 +1610,26 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -882,10 +882,10 @@
         <v>100</v>
       </c>
       <c r="M14" s="15">
+        <v>-60</v>
+      </c>
+      <c r="N14" s="15">
         <v>-50</v>
-      </c>
-      <c r="N14" s="15">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>87.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>1400</v>
+        <v>650</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
         <v>36</v>
       </c>
       <c r="H16" s="15">
-        <v>-63.888888888888</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J16" s="14">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K16" s="15">
-        <v>-36.144578313253</v>
+        <v>-38.043478260869</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.372093023255</v>
+        <v>-38.043478260869</v>
       </c>
       <c r="M16" s="15">
-        <v>29.268292682926</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.956521739130</v>
+        <v>-77.992277992278</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>18.181818181818</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="F17" s="14">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.111111111111</v>
+        <v>-28.813559322033</v>
       </c>
       <c r="I17" s="14">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="J17" s="14">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-5.673758865248</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.823529411764</v>
+        <v>-13.071895424836</v>
       </c>
       <c r="M17" s="15">
-        <v>153.061224489796</v>
+        <v>155.769230769231</v>
       </c>
       <c r="N17" s="15">
-        <v>-32.608695652173</v>
+        <v>-35.436893203883</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-57.142857142857</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.052631578947</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-4</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.727272727272</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="M18" s="15">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="N18" s="15">
-        <v>-75</v>
+        <v>-76.681614349775</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-15</v>
+        <v>-27.906976744186</v>
       </c>
       <c r="I19" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J19" s="14">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K19" s="15">
-        <v>-27.722772277227</v>
+        <v>-27.927927927927</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.606837606837</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M19" s="15">
-        <v>73.809523809523</v>
+        <v>73.913043478260</v>
       </c>
       <c r="N19" s="15">
-        <v>21.666666666666</v>
+        <v>17.647058823529</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>6</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>10</v>
-      </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>-38.095238095238</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J20" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K20" s="15">
-        <v>-46.938775510204</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="L20" s="15">
-        <v>-44.680851063829</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M20" s="15">
-        <v>4</v>
+        <v>18.518518518518</v>
       </c>
       <c r="N20" s="15">
-        <v>-73.737373737373</v>
+        <v>-72.173913043478</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,51 +1142,51 @@
         <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18">
-        <v>-39.583333333333</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="F21" s="17">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G21" s="17">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.714285714285</v>
+        <v>-32.044198895027</v>
       </c>
       <c r="I21" s="17">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="J21" s="17">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.831325301204</v>
+        <v>-19.172113289760</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.557522123893</v>
+        <v>-25.651302605210</v>
       </c>
       <c r="M21" s="18">
-        <v>83.333333333333</v>
+        <v>78.365384615384</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.113256113256</v>
+        <v>-58.173618940248</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
@@ -1198,19 +1198,19 @@
         <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M22" s="15">
         <v>0</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
         <v>-25</v>
       </c>
       <c r="F23" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H23" s="15">
-        <v>15.384615384615</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="I23" s="14">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K23" s="15">
-        <v>13.043478260869</v>
+        <v>9.259259259259</v>
       </c>
       <c r="L23" s="15">
-        <v>-38.823529411764</v>
+        <v>-38.541666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>36.842105263157</v>
+        <v>47.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>4.761904761904</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>8.045977011494</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I24" s="14">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="J24" s="14">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="K24" s="15">
-        <v>6.451612903225</v>
+        <v>4.048582995951</v>
       </c>
       <c r="L24" s="15">
-        <v>1.315789473684</v>
+        <v>3.629032258064</v>
       </c>
       <c r="M24" s="15">
-        <v>62.676056338028</v>
+        <v>63.694267515923</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
         <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J25" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K25" s="15">
-        <v>24.390243902439</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L25" s="15">
-        <v>41.666666666666</v>
+        <v>36.842105263157</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>91.666666666666</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="F26" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H26" s="15">
-        <v>23.529411764705</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I26" s="14">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="J26" s="14">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.128205128205</v>
+        <v>-9.340659340659</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.303030303030</v>
+        <v>-13.612565445026</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.853932584269</v>
+        <v>-14.948453608247</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L27" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>77.777777777777</v>
+        <v>63.636363636363</v>
       </c>
       <c r="L28" s="15">
-        <v>45.454545454545</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1497,10 +1497,10 @@
         <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-60</v>
+        <v>-64.705882352941</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,10 +1520,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1538,10 +1538,10 @@
         <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-70.588235294117</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -902,31 +902,31 @@
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-20</v>
+        <v>-80</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M15" s="15">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>25</v>
+        <v>15.384615384615</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-55.555555555555</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-55.555555555555</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="I16" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.043478260869</v>
+        <v>-37.373737373737</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.043478260869</v>
+        <v>-37.373737373737</v>
       </c>
       <c r="M16" s="15">
-        <v>11.764705882352</v>
+        <v>14.814814814814</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.992277992278</v>
+        <v>-78.397212543554</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-52.941176470588</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G17" s="14">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>-28.813559322033</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="I17" s="14">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="J17" s="14">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.673758865248</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="L17" s="15">
-        <v>-13.071895424836</v>
+        <v>-6.832298136645</v>
       </c>
       <c r="M17" s="15">
-        <v>155.769230769231</v>
+        <v>167.857142857143</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.436893203883</v>
+        <v>-30.875576036866</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
@@ -1034,22 +1034,22 @@
         <v>-5.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.454545454545</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.864406779661</v>
+        <v>-15.942028985507</v>
       </c>
       <c r="M18" s="15">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.681614349775</v>
+        <v>-77.075098814229</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>-27.906976744186</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="I19" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J19" s="14">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K19" s="15">
-        <v>-27.927927927927</v>
+        <v>-29.508196721311</v>
       </c>
       <c r="L19" s="15">
-        <v>-38.461538461538</v>
+        <v>-40.689655172413</v>
       </c>
       <c r="M19" s="15">
-        <v>73.913043478260</v>
+        <v>72</v>
       </c>
       <c r="N19" s="15">
-        <v>17.647058823529</v>
+        <v>17.808219178082</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
         <v>6</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I20" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K20" s="15">
-        <v>-37.254901960784</v>
+        <v>-38.596491228070</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.461538461538</v>
+        <v>-40.677966101694</v>
       </c>
       <c r="M20" s="15">
-        <v>18.518518518518</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-72.173913043478</v>
+        <v>-72.440944881889</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-34.090909090909</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F21" s="17">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H21" s="18">
-        <v>-32.044198895027</v>
+        <v>-25.568181818181</v>
       </c>
       <c r="I21" s="17">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="J21" s="17">
-        <v>459</v>
+        <v>501</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.172113289760</v>
+        <v>-18.562874251497</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.651302605210</v>
+        <v>-25.547445255474</v>
       </c>
       <c r="M21" s="18">
-        <v>78.365384615384</v>
+        <v>79.735682819383</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.173618940248</v>
+        <v>-58.153846153846</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G23" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>-3.571428571428</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="I23" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J23" s="14">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K23" s="15">
-        <v>9.259259259259</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L23" s="15">
-        <v>-38.541666666666</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="M23" s="15">
-        <v>47.5</v>
+        <v>42.222222222222</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.333333333333</v>
+        <v>30.434782608695</v>
       </c>
       <c r="F24" s="14">
         <v>96</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.882352941176</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I24" s="14">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="J24" s="14">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="K24" s="15">
-        <v>4.048582995951</v>
+        <v>4.074074074074</v>
       </c>
       <c r="L24" s="15">
-        <v>3.629032258064</v>
+        <v>4.460966542750</v>
       </c>
       <c r="M24" s="15">
-        <v>63.694267515923</v>
+        <v>56.983240223463</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-14.285714285714</v>
+        <v>15</v>
       </c>
       <c r="I25" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J25" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K25" s="15">
-        <v>18.181818181818</v>
+        <v>29.787234042553</v>
       </c>
       <c r="L25" s="15">
-        <v>36.842105263157</v>
+        <v>48.780487804878</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>-34.615384615384</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="14">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H26" s="15">
-        <v>4.545454545454</v>
+        <v>-10.126582278481</v>
       </c>
       <c r="I26" s="14">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J26" s="14">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.340659340659</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.612565445026</v>
+        <v>-10.784313725490</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.948453608247</v>
+        <v>-12.918660287081</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>80</v>
+        <v>63.636363636363</v>
       </c>
       <c r="L27" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>63.636363636363</v>
+        <v>72.727272727272</v>
       </c>
       <c r="L28" s="15">
-        <v>38.461538461538</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1497,10 +1497,10 @@
         <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-64.705882352941</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,10 +1520,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1538,10 +1538,10 @@
         <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-70.588235294117</v>
+        <v>-72.222222222222</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="15">
         <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-80</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
@@ -926,7 +926,7 @@
         <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>15.384615384615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-28.571428571428</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F16" s="14">
         <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H16" s="15">
-        <v>-39.393939393939</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J16" s="14">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.373737373737</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.373737373737</v>
+        <v>-33.009708737864</v>
       </c>
       <c r="M16" s="15">
-        <v>14.814814814814</v>
+        <v>21.052631578947</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.397212543554</v>
+        <v>-77.152317880794</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-7.142857142857</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="15">
-        <v>-17.857142857142</v>
+        <v>-1.754385964912</v>
       </c>
       <c r="I17" s="14">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="J17" s="14">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.225806451612</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.832298136645</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="M17" s="15">
-        <v>167.857142857143</v>
+        <v>183.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-30.875576036866</v>
+        <v>-26.406926406926</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.555555555555</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I18" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J18" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.942028985507</v>
+        <v>-20</v>
       </c>
       <c r="M18" s="15">
         <v>100</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.075098814229</v>
+        <v>-78.021978021978</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-54.545454545454</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.829268292682</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="I19" s="14">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="J19" s="14">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K19" s="15">
-        <v>-29.508196721311</v>
+        <v>-22.65625</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.689655172413</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="M19" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="N19" s="15">
-        <v>17.808219178082</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>-30.434782608695</v>
+        <v>-44</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K20" s="15">
-        <v>-38.596491228070</v>
+        <v>-42.1875</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.677966101694</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="M20" s="15">
-        <v>16.666666666666</v>
+        <v>15.625</v>
       </c>
       <c r="N20" s="15">
-        <v>-72.440944881889</v>
+        <v>-73.758865248227</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,60 +1139,60 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.809523809523</v>
+        <v>2.439024390243</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.568181818181</v>
+        <v>-22.285714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="J21" s="17">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.562874251497</v>
+        <v>-16.605166051660</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.547445255474</v>
+        <v>-22.866894197952</v>
       </c>
       <c r="M21" s="18">
-        <v>79.735682819383</v>
+        <v>86.776859504132</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.153846153846</v>
+        <v>-56.829035339064</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
       </c>
       <c r="H22" s="15">
         <v>100</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G23" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H23" s="15">
-        <v>-19.230769230769</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="I23" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="J23" s="14">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K23" s="15">
-        <v>3.225806451612</v>
+        <v>4.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>-37.254901960784</v>
+        <v>-31.775700934579</v>
       </c>
       <c r="M23" s="15">
-        <v>42.222222222222</v>
+        <v>55.319148936170</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>29</v>
+      </c>
+      <c r="D24" s="14">
         <v>30</v>
       </c>
-      <c r="D24" s="14">
-        <v>23</v>
-      </c>
       <c r="E24" s="15">
-        <v>30.434782608695</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G24" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.040816326530</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="I24" s="14">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="J24" s="14">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="K24" s="15">
-        <v>4.074074074074</v>
+        <v>3.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>4.460966542750</v>
+        <v>7.638888888888</v>
       </c>
       <c r="M24" s="15">
-        <v>56.983240223463</v>
+        <v>64.021164021164</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>200</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J25" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K25" s="15">
-        <v>29.787234042553</v>
+        <v>19.230769230769</v>
       </c>
       <c r="L25" s="15">
-        <v>48.780487804878</v>
+        <v>51.219512195122</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-14.285714285714</v>
+        <v>26.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G26" s="14">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.126582278481</v>
+        <v>2.702702702702</v>
       </c>
       <c r="I26" s="14">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="J26" s="14">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.344827586206</v>
+        <v>-8.715596330275</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.784313725490</v>
+        <v>-8.715596330275</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.918660287081</v>
+        <v>-9.132420091324</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
         <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
-        <v>5</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-80</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
@@ -1412,7 +1412,7 @@
         <v>63.636363636363</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>72.727272727272</v>
+        <v>53.846153846153</v>
       </c>
       <c r="L28" s="15">
-        <v>11.764705882352</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1497,10 +1497,10 @@
         <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="N29" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.421052631578</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1538,10 +1538,10 @@
         <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N30" s="15">
-        <v>-72.222222222222</v>
+        <v>-73.684210526315</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -923,10 +923,10 @@
         <v>7.142857142857</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.5</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="I16" s="14">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J16" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.285714285714</v>
+        <v>-32.456140350877</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.009708737864</v>
+        <v>-28.037383177570</v>
       </c>
       <c r="M16" s="15">
-        <v>21.052631578947</v>
+        <v>24.193548387096</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.152317880794</v>
+        <v>-76.595744680851</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>13.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
+        <v>49</v>
+      </c>
+      <c r="G17" s="14">
         <v>56</v>
       </c>
-      <c r="G17" s="14">
-        <v>57</v>
-      </c>
       <c r="H17" s="15">
-        <v>-1.754385964912</v>
+        <v>-12.5</v>
       </c>
       <c r="I17" s="14">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J17" s="14">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-1.111111111111</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.162790697674</v>
+        <v>-9.183673469387</v>
       </c>
       <c r="M17" s="15">
-        <v>183.333333333333</v>
+        <v>161.764705882353</v>
       </c>
       <c r="N17" s="15">
-        <v>-26.406926406926</v>
+        <v>-26.748971193415</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-71.428571428571</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
         <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-36.363636363636</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I18" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J18" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K18" s="15">
-        <v>-7.692307692307</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-20</v>
+        <v>-16.455696202531</v>
       </c>
       <c r="M18" s="15">
-        <v>100</v>
+        <v>94.117647058823</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.021978021978</v>
+        <v>-78.145695364238</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>12</v>
+      </c>
+      <c r="D19" s="14">
         <v>13</v>
       </c>
-      <c r="D19" s="14">
-        <v>6</v>
-      </c>
       <c r="E19" s="15">
-        <v>116.666666666667</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.571428571428</v>
+        <v>-12.5</v>
       </c>
       <c r="I19" s="14">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J19" s="14">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.65625</v>
+        <v>-22.695035460992</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.735849056603</v>
+        <v>-34.730538922155</v>
       </c>
       <c r="M19" s="15">
-        <v>80</v>
+        <v>81.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>23.75</v>
+        <v>26.744186046511</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.142857142857</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-44</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K20" s="15">
-        <v>-42.1875</v>
+        <v>-41.428571428571</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.322580645161</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="M20" s="15">
-        <v>15.625</v>
+        <v>28.125</v>
       </c>
       <c r="N20" s="15">
-        <v>-73.758865248227</v>
+        <v>-73.376623376623</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>2.439024390243</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G21" s="17">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.285714285714</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="I21" s="17">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="J21" s="17">
-        <v>542</v>
+        <v>587</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.605166051660</v>
+        <v>-16.865417376490</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.866894197952</v>
+        <v>-22.044728434504</v>
       </c>
       <c r="M21" s="18">
-        <v>86.776859504132</v>
+        <v>83.458646616541</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.829035339064</v>
+        <v>-57.042253521126</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1207,10 +1207,10 @@
         <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F23" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>-17.857142857142</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="I23" s="14">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J23" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K23" s="15">
-        <v>4.285714285714</v>
+        <v>6.493506493506</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.775700934579</v>
+        <v>-26.785714285714</v>
       </c>
       <c r="M23" s="15">
-        <v>55.319148936170</v>
+        <v>70.833333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.333333333333</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F24" s="14">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
         <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.923076923076</v>
+        <v>-5.769230769230</v>
       </c>
       <c r="I24" s="14">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="J24" s="14">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="K24" s="15">
-        <v>3.333333333333</v>
+        <v>2.492211838006</v>
       </c>
       <c r="L24" s="15">
-        <v>7.638888888888</v>
+        <v>7.868852459016</v>
       </c>
       <c r="M24" s="15">
-        <v>64.021164021164</v>
+        <v>64.5</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J25" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K25" s="15">
-        <v>19.230769230769</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>51.219512195122</v>
+        <v>40.425531914893</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>26.666666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="F26" s="14">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H26" s="15">
-        <v>2.702702702702</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="I26" s="14">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="J26" s="14">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.715596330275</v>
+        <v>-9.401709401709</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.715596330275</v>
+        <v>-9.012875536480</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.132420091324</v>
+        <v>-12.033195020746</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1412,7 +1412,7 @@
         <v>63.636363636363</v>
       </c>
       <c r="L27" s="15">
-        <v>-5.263157894736</v>
+        <v>-10</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,22 +1438,22 @@
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-28.571428571428</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>53.846153846153</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>11.111111111111</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-68.421052631578</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-44.444444444444</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N30" s="15">
-        <v>-73.684210526315</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -885,15 +885,15 @@
         <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="L15" s="15">
-        <v>7.142857142857</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="N15" s="15">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>26</v>
+      </c>
+      <c r="G16" s="14">
+        <v>34</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-23.529411764705</v>
+      </c>
+      <c r="I16" s="14">
+        <v>84</v>
+      </c>
+      <c r="J16" s="14">
+        <v>126</v>
+      </c>
+      <c r="K16" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="F16" s="14">
-        <v>23</v>
-      </c>
-      <c r="G16" s="14">
-        <v>31</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-25.806451612903</v>
-      </c>
-      <c r="I16" s="14">
-        <v>77</v>
-      </c>
-      <c r="J16" s="14">
-        <v>114</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-32.456140350877</v>
-      </c>
       <c r="L16" s="15">
-        <v>-28.037383177570</v>
+        <v>-26.956521739130</v>
       </c>
       <c r="M16" s="15">
-        <v>24.193548387096</v>
+        <v>25.373134328358</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.595744680851</v>
+        <v>-76</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.5</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I17" s="14">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="J17" s="14">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.111111111111</v>
+        <v>-4.102564102564</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.183673469387</v>
+        <v>-10.096153846153</v>
       </c>
       <c r="M17" s="15">
-        <v>161.764705882353</v>
+        <v>159.722222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-26.748971193415</v>
+        <v>-29.166666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-14.285714285714</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-22.727272727272</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J18" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K18" s="15">
-        <v>-8.333333333333</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="L18" s="15">
-        <v>-16.455696202531</v>
+        <v>-20.238095238095</v>
       </c>
       <c r="M18" s="15">
-        <v>94.117647058823</v>
+        <v>76.315789473684</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.145695364238</v>
+        <v>-79.320987654321</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.5</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="I19" s="14">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J19" s="14">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.695035460992</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.730538922155</v>
+        <v>-35.028248587570</v>
       </c>
       <c r="M19" s="15">
-        <v>81.666666666666</v>
+        <v>85.483870967741</v>
       </c>
       <c r="N19" s="15">
-        <v>26.744186046511</v>
+        <v>30.681818181818</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-23.809523809523</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J20" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K20" s="15">
-        <v>-41.428571428571</v>
+        <v>-44</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.870967741935</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M20" s="15">
-        <v>28.125</v>
+        <v>20</v>
       </c>
       <c r="N20" s="15">
-        <v>-73.376623376623</v>
+        <v>-75.581395348837</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G21" s="17">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.604651162790</v>
+        <v>-22.159090909090</v>
       </c>
       <c r="I21" s="17">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="J21" s="17">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.865417376490</v>
+        <v>-19.055118110236</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.044728434504</v>
+        <v>-23.053892215568</v>
       </c>
       <c r="M21" s="18">
-        <v>83.458646616541</v>
+        <v>80.985915492957</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.042253521126</v>
+        <v>-57.937806873977</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>42.857142857142</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F23" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.903225806451</v>
+        <v>-31.25</v>
       </c>
       <c r="I23" s="14">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J23" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K23" s="15">
-        <v>6.493506493506</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.785714285714</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M23" s="15">
-        <v>70.833333333333</v>
+        <v>64.705882352941</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.809523809523</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.769230769230</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I24" s="14">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="J24" s="14">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="K24" s="15">
-        <v>2.492211838006</v>
+        <v>-1.420454545454</v>
       </c>
       <c r="L24" s="15">
-        <v>7.868852459016</v>
+        <v>4.204204204204</v>
       </c>
       <c r="M24" s="15">
-        <v>64.5</v>
+        <v>62.910798122065</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J25" s="14">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K25" s="15">
-        <v>17.857142857142</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L25" s="15">
-        <v>40.425531914893</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>-18.75</v>
+        <v>10</v>
       </c>
       <c r="F26" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G26" s="14">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.820512820512</v>
+        <v>-1.388888888888</v>
       </c>
       <c r="I26" s="14">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="J26" s="14">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.401709401709</v>
+        <v>-8.267716535433</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.012875536480</v>
+        <v>-7.171314741035</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.033195020746</v>
+        <v>-9.338521400778</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
         <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>63.636363636363</v>
+        <v>81.818181818181</v>
       </c>
       <c r="L27" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M29" s="15">
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-70</v>
+        <v>-73.913043478260</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M30" s="15">
         <v>-54.545454545454</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,21 +879,21 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M14" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,11 +904,11 @@
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>17</v>
@@ -920,13 +920,13 @@
         <v>70</v>
       </c>
       <c r="L15" s="15">
-        <v>21.428571428571</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M15" s="15">
         <v>240</v>
       </c>
       <c r="N15" s="15">
-        <v>6.25</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.529411764705</v>
+        <v>-32.5</v>
       </c>
       <c r="I16" s="14">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J16" s="14">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.251798561151</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.956521739130</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>25.373134328358</v>
+        <v>21.621621621621</v>
       </c>
       <c r="N16" s="15">
-        <v>-76</v>
+        <v>-75.609756097561</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-46.666666666666</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.407407407407</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="I17" s="14">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="J17" s="14">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.102564102564</v>
+        <v>-2.912621359223</v>
       </c>
       <c r="L17" s="15">
-        <v>-10.096153846153</v>
+        <v>-8.256880733944</v>
       </c>
       <c r="M17" s="15">
-        <v>159.722222222222</v>
+        <v>159.74025974026</v>
       </c>
       <c r="N17" s="15">
-        <v>-29.166666666666</v>
+        <v>-27.797833935018</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-85.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
         <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.666666666666</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J18" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K18" s="15">
-        <v>-15.189873417721</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="L18" s="15">
-        <v>-20.238095238095</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>76.315789473684</v>
+        <v>81.578947368421</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.320987654321</v>
+        <v>-79.525222551928</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.820512820512</v>
+        <v>12.195121951219</v>
       </c>
       <c r="I19" s="14">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="J19" s="14">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.333333333333</v>
+        <v>-16.564417177914</v>
       </c>
       <c r="L19" s="15">
-        <v>-35.028248587570</v>
+        <v>-27.659574468085</v>
       </c>
       <c r="M19" s="15">
-        <v>85.483870967741</v>
+        <v>94.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>30.681818181818</v>
+        <v>44.680851063829</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>-54.166666666666</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="I20" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K20" s="15">
-        <v>-44</v>
+        <v>-51.190476190476</v>
       </c>
       <c r="L20" s="15">
-        <v>-39.130434782608</v>
+        <v>-46.052631578947</v>
       </c>
       <c r="M20" s="15">
-        <v>20</v>
+        <v>13.888888888888</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.581395348837</v>
+        <v>-77.956989247311</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-24.489795918367</v>
       </c>
       <c r="F21" s="17">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G21" s="17">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.159090909090</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="I21" s="17">
-        <v>514</v>
+        <v>556</v>
       </c>
       <c r="J21" s="17">
-        <v>635</v>
+        <v>684</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.055118110236</v>
+        <v>-18.713450292397</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.053892215568</v>
+        <v>-22.346368715083</v>
       </c>
       <c r="M21" s="18">
-        <v>80.985915492957</v>
+        <v>82.295081967213</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.937806873977</v>
+        <v>-56.932610379550</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-77.777777777777</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
         <v>22</v>
       </c>
       <c r="G23" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H23" s="15">
-        <v>-31.25</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="I23" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J23" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.325581395348</v>
+        <v>-1.123595505617</v>
       </c>
       <c r="L23" s="15">
-        <v>-29.411764705882</v>
+        <v>-30.708661417322</v>
       </c>
       <c r="M23" s="15">
-        <v>64.705882352941</v>
+        <v>51.724137931034</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-45.161290322580</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.523809523809</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I24" s="14">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="J24" s="14">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.420454545454</v>
+        <v>-3.421052631578</v>
       </c>
       <c r="L24" s="15">
-        <v>4.204204204204</v>
+        <v>1.381215469613</v>
       </c>
       <c r="M24" s="15">
-        <v>62.910798122065</v>
+        <v>62.389380530973</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-55.555555555555</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H25" s="15">
-        <v>-14.285714285714</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J25" s="14">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K25" s="15">
-        <v>7.692307692307</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="L25" s="15">
-        <v>42.857142857142</v>
+        <v>37.037037037037</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>10</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F26" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G26" s="14">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.388888888888</v>
+        <v>2.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="J26" s="14">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.267716535433</v>
+        <v>-9.157509157509</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.171314741035</v>
+        <v>-8.487084870848</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.338521400778</v>
+        <v>-7.116104868913</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>81.818181818181</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
+        <v>200</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="I28" s="14">
+        <v>27</v>
+      </c>
+      <c r="J28" s="14">
+        <v>18</v>
+      </c>
+      <c r="K28" s="15">
         <v>50</v>
       </c>
-      <c r="F28" s="14">
-        <v>6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
-      </c>
-      <c r="I28" s="14">
-        <v>24</v>
-      </c>
-      <c r="J28" s="14">
-        <v>17</v>
-      </c>
-      <c r="K28" s="15">
-        <v>41.176470588235</v>
-      </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-73.913043478260</v>
+        <v>-70.833333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
         <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-54.545454545454</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N30" s="15">
-        <v>-78.260869565217</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -895,32 +895,32 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>17</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>70</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>13.333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="M15" s="15">
         <v>240</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-53.846153846153</v>
+        <v>-12.5</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H16" s="15">
-        <v>-32.5</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I16" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J16" s="14">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.251798561151</v>
+        <v>-34.013605442176</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.571428571428</v>
+        <v>-29.710144927536</v>
       </c>
       <c r="M16" s="15">
-        <v>21.621621621621</v>
+        <v>19.753086419753</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.609756097561</v>
+        <v>-75.128205128205</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E17" s="15">
-        <v>18.181818181818</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F17" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.843137254901</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="I17" s="14">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="J17" s="14">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.912621359223</v>
+        <v>-4.741379310344</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.256880733944</v>
+        <v>-6.355932203389</v>
       </c>
       <c r="M17" s="15">
-        <v>159.74025974026</v>
+        <v>166.265060240964</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.797833935018</v>
+        <v>-24.573378839590</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H18" s="15">
-        <v>-54.166666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I18" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J18" s="14">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K18" s="15">
-        <v>-15.853658536585</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-25</v>
+        <v>-19.587628865979</v>
       </c>
       <c r="M18" s="15">
-        <v>81.578947368421</v>
+        <v>95</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.525222551928</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>23.076923076923</v>
+        <v>85.714285714285</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>12.195121951219</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="J19" s="14">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.564417177914</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.659574468085</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M19" s="15">
-        <v>94.285714285714</v>
+        <v>111.267605633803</v>
       </c>
       <c r="N19" s="15">
-        <v>44.680851063829</v>
+        <v>45.631067961165</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>-74.074074074074</v>
+        <v>-76</v>
       </c>
       <c r="I20" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K20" s="15">
-        <v>-51.190476190476</v>
+        <v>-51.685393258427</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.052631578947</v>
+        <v>-46.913580246913</v>
       </c>
       <c r="M20" s="15">
-        <v>13.888888888888</v>
+        <v>4.878048780487</v>
       </c>
       <c r="N20" s="15">
-        <v>-77.956989247311</v>
+        <v>-78.172588832487</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18">
-        <v>-24.489795918367</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="F21" s="17">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="G21" s="17">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.950819672131</v>
+        <v>-22.613065326633</v>
       </c>
       <c r="I21" s="17">
-        <v>556</v>
+        <v>609</v>
       </c>
       <c r="J21" s="17">
-        <v>684</v>
+        <v>741</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.713450292397</v>
+        <v>-17.813765182186</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.346368715083</v>
+        <v>-20.599739243807</v>
       </c>
       <c r="M21" s="18">
-        <v>82.295081967213</v>
+        <v>86.809815950920</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.932610379550</v>
+        <v>-55.286343612334</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H23" s="15">
-        <v>-18.518518518518</v>
+        <v>-24</v>
       </c>
       <c r="I23" s="14">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J23" s="14">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K23" s="15">
-        <v>-1.123595505617</v>
+        <v>-4.210526315789</v>
       </c>
       <c r="L23" s="15">
-        <v>-30.708661417322</v>
+        <v>-30</v>
       </c>
       <c r="M23" s="15">
-        <v>51.724137931034</v>
+        <v>46.774193548387</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.571428571428</v>
+        <v>3.846153846153</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.727272727272</v>
+        <v>-23.584905660377</v>
       </c>
       <c r="I24" s="14">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="J24" s="14">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.421052631578</v>
+        <v>-2.463054187192</v>
       </c>
       <c r="L24" s="15">
-        <v>1.381215469613</v>
+        <v>5.039787798408</v>
       </c>
       <c r="M24" s="15">
-        <v>62.389380530973</v>
+        <v>62.962962962963</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>-56.666666666666</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="I25" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J25" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K25" s="15">
-        <v>-3.896103896103</v>
+        <v>-6.024096385542</v>
       </c>
       <c r="L25" s="15">
-        <v>37.037037037037</v>
+        <v>36.842105263157</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>-21.052631578947</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F26" s="14">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H26" s="15">
-        <v>2.857142857142</v>
+        <v>-11.688311688311</v>
       </c>
       <c r="I26" s="14">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="J26" s="14">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.157509157509</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.487084870848</v>
+        <v>-8.934707903780</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.116104868913</v>
+        <v>-6.360424028268</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>81.818181818181</v>
+        <v>53.846153846153</v>
       </c>
       <c r="L27" s="15">
-        <v>-4.761904761904</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
         <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>17.391304347826</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L29" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M29" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-70.833333333333</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="14">
         <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-45.454545454545</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-042pct.xlsx
+++ b/data/source/weekly/cs-en-us-042pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J15" s="14">
         <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>41.666666666666</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>6.25</v>
+        <v>18.75</v>
       </c>
       <c r="M15" s="15">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="N15" s="15">
-        <v>-15</v>
+        <v>-13.636363636363</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E16" s="15">
-        <v>-12.5</v>
+        <v>-68.75</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H16" s="15">
-        <v>-38.095238095238</v>
+        <v>-51.020408163265</v>
       </c>
       <c r="I16" s="14">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J16" s="14">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.013605442176</v>
+        <v>-37.423312883435</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.710144927536</v>
+        <v>-31.081081081081</v>
       </c>
       <c r="M16" s="15">
-        <v>19.753086419753</v>
+        <v>21.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.128205128205</v>
+        <v>-75.362318840579</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>-23.076923076923</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G17" s="14">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.903225806451</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I17" s="14">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="J17" s="14">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.741379310344</v>
+        <v>-6.640625</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.355932203389</v>
+        <v>-8.076923076923</v>
       </c>
       <c r="M17" s="15">
-        <v>166.265060240964</v>
+        <v>159.782608695652</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.573378839590</v>
+        <v>-25.078369905956</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-30.769230769230</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I18" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J18" s="14">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.285714285714</v>
+        <v>-10.752688172043</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.587628865979</v>
+        <v>-19.417475728155</v>
       </c>
       <c r="M18" s="15">
-        <v>95</v>
+        <v>88.636363636363</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.777777777777</v>
+        <v>-77.866666666666</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>85.714285714285</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>14.285714285714</v>
+        <v>6.382978723404</v>
       </c>
       <c r="I19" s="14">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="J19" s="14">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.764705882352</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.242424242424</v>
+        <v>-21.904761904761</v>
       </c>
       <c r="M19" s="15">
-        <v>111.267605633803</v>
+        <v>118.666666666667</v>
       </c>
       <c r="N19" s="15">
-        <v>45.631067961165</v>
+        <v>47.747747747747</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,28 +1110,28 @@
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-76</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J20" s="14">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K20" s="15">
-        <v>-51.685393258427</v>
+        <v>-51.063829787234</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.913580246913</v>
+        <v>-47.727272727272</v>
       </c>
       <c r="M20" s="15">
-        <v>4.878048780487</v>
+        <v>9.523809523809</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.172588832487</v>
+        <v>-77.560975609756</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.771929824561</v>
+        <v>-35.384615384615</v>
       </c>
       <c r="F21" s="17">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G21" s="17">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.613065326633</v>
+        <v>-26.484018264840</v>
       </c>
       <c r="I21" s="17">
-        <v>609</v>
+        <v>656</v>
       </c>
       <c r="J21" s="17">
-        <v>741</v>
+        <v>806</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.813765182186</v>
+        <v>-18.610421836228</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.599739243807</v>
+        <v>-20.581113801452</v>
       </c>
       <c r="M21" s="18">
-        <v>86.809815950920</v>
+        <v>89.048991354466</v>
       </c>
       <c r="N21" s="18">
-        <v>-55.286343612334</v>
+        <v>-54.883081155433</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-24</v>
+        <v>-56.25</v>
       </c>
       <c r="I23" s="14">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J23" s="14">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.210526315789</v>
+        <v>-11.926605504587</v>
       </c>
       <c r="L23" s="15">
-        <v>-30</v>
+        <v>-30.935251798561</v>
       </c>
       <c r="M23" s="15">
-        <v>46.774193548387</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>3.846153846153</v>
+        <v>12</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.584905660377</v>
+        <v>-16.363636363636</v>
       </c>
       <c r="I24" s="14">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="J24" s="14">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.463054187192</v>
+        <v>-1.624129930394</v>
       </c>
       <c r="L24" s="15">
-        <v>5.039787798408</v>
+        <v>8.163265306122</v>
       </c>
       <c r="M24" s="15">
-        <v>62.962962962963</v>
+        <v>65.625</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H25" s="15">
-        <v>-51.612903225806</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="I25" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J25" s="14">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.024096385542</v>
+        <v>-3.529411764705</v>
       </c>
       <c r="L25" s="15">
-        <v>36.842105263157</v>
+        <v>38.983050847457</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-22.727272727272</v>
+        <v>118.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.688311688311</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="J26" s="14">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.169491525423</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.934707903780</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.360424028268</v>
+        <v>-0.687285223367</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J27" s="14">
         <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>53.846153846153</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L27" s="15">
-        <v>-9.090909090909</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>50</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>42.857142857142</v>
+        <v>120</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="14">
         <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L28" s="15">
-        <v>11.111111111111</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>14.285714285714</v>
       </c>
       <c r="M29" s="15">
-        <v>-46.666666666666</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="N29" s="15">
-        <v>-68</v>
+        <v>-72.413793103448</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-46.153846153846</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-72</v>
+        <v>-75.862068965517</v>
       </c>
     </row>
     <row r="31" spans="1:14">
